--- a/assignment3/data/trainingdataset_ontario_budgets_v20_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v20_llm_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DF77FC-EFB8-3543-B5A5-B55BCFDA0807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8281327-4D5F-D348-8FD4-DDF97035BAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5120" yWindow="1140" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="623">
   <si>
     <t>document</t>
   </si>
@@ -2607,14 +2607,7 @@
     <t>As required by the Board of Governors, Lakehead University presents a balanced operating budget. The budget planning process for 2022-23 fully reflects our integrated budget development model and exhibits a transparent, consultative and accountable integrated budgeting process. Despite significant financial changes and enrolment pressures, Lakehead has been able to mitigate funding shortfalls.</t>
   </si>
   <si>
-    <t>The pandemic has necessitated rigorous budget measures and, for the immediate
-future as we address the lasting impact of COVID-19, this approach has been maintained. The additional budget controls that we collectively undertook during the last two years have assisted addressing the realities faced by the global pandemic, and have assisted mitigating shortfalls while ensuring that Lakehead remains financially sustainable and viable moving through and beyond the current year. Some of these additional budget controls will continue during 2022-23 as necessary.</t>
-  </si>
-  <si>
     <t>lakehead_2022_5</t>
-  </si>
-  <si>
-    <t>lakehead_2022_6</t>
   </si>
   <si>
     <t>lakehead_2023</t>
@@ -3454,7 +3447,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U278"/>
+  <dimension ref="A1:U277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -14385,7 +14378,7 @@
         <v>539</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>540</v>
@@ -14420,22 +14413,25 @@
     </row>
     <row r="242" spans="1:15">
       <c r="A242" s="4" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B242" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C242" s="24" t="s">
         <v>543</v>
       </c>
-      <c r="C242" s="24" t="s">
-        <v>541</v>
-      </c>
       <c r="F242" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G242" s="23">
+        <v>1</v>
       </c>
       <c r="I242" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J242" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>538</v>
@@ -14444,7 +14440,7 @@
         <v>13</v>
       </c>
       <c r="M242" s="4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="N242" s="4">
         <v>1</v>
@@ -14455,22 +14451,22 @@
     </row>
     <row r="243" spans="1:15">
       <c r="A243" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C243" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="B243" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="C243" s="24" t="s">
-        <v>545</v>
-      </c>
       <c r="F243" s="13">
         <v>1</v>
       </c>
       <c r="G243" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J243" s="4">
         <v>5</v>
@@ -14493,13 +14489,13 @@
     </row>
     <row r="244" spans="1:15">
       <c r="A244" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F244" s="13">
         <v>1</v>
@@ -14508,7 +14504,7 @@
         <v>0</v>
       </c>
       <c r="I244" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J244" s="4">
         <v>5</v>
@@ -14531,22 +14527,22 @@
     </row>
     <row r="245" spans="1:15">
       <c r="A245" s="4" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F245" s="13">
         <v>1</v>
       </c>
       <c r="G245" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J245" s="4">
         <v>5</v>
@@ -14558,7 +14554,7 @@
         <v>13</v>
       </c>
       <c r="M245" s="4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="N245" s="4">
         <v>1</v>
@@ -14569,10 +14565,10 @@
     </row>
     <row r="246" spans="1:15">
       <c r="A246" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B246" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="B246" s="4" t="s">
-        <v>551</v>
       </c>
       <c r="C246" s="9" t="s">
         <v>553</v>
@@ -14584,7 +14580,7 @@
         <v>1</v>
       </c>
       <c r="I246" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J246" s="4">
         <v>5</v>
@@ -14607,14 +14603,14 @@
     </row>
     <row r="247" spans="1:15">
       <c r="A247" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B247" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C247" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="C247" s="9" t="s">
-        <v>555</v>
-      </c>
       <c r="F247" s="13">
         <v>1</v>
       </c>
@@ -14622,7 +14618,7 @@
         <v>1</v>
       </c>
       <c r="I247" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J247" s="4">
         <v>5</v>
@@ -14645,22 +14641,22 @@
     </row>
     <row r="248" spans="1:15">
       <c r="A248" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F248" s="13">
         <v>1</v>
       </c>
       <c r="G248" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I248" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J248" s="4">
         <v>5</v>
@@ -14683,13 +14679,13 @@
     </row>
     <row r="249" spans="1:15">
       <c r="A249" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C249" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F249" s="13">
         <v>1</v>
@@ -14698,7 +14694,7 @@
         <v>0</v>
       </c>
       <c r="I249" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J249" s="4">
         <v>5</v>
@@ -14721,25 +14717,25 @@
     </row>
     <row r="250" spans="1:15">
       <c r="A250" s="4" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F250" s="13">
         <v>1</v>
       </c>
       <c r="G250" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I250" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J250" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>538</v>
@@ -14748,7 +14744,7 @@
         <v>13</v>
       </c>
       <c r="M250" s="4">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="N250" s="4">
         <v>1</v>
@@ -14759,10 +14755,10 @@
     </row>
     <row r="251" spans="1:15">
       <c r="A251" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B251" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="B251" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>564</v>
@@ -14774,7 +14770,7 @@
         <v>1</v>
       </c>
       <c r="I251" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J251" s="4">
         <v>8</v>
@@ -14797,14 +14793,14 @@
     </row>
     <row r="252" spans="1:15">
       <c r="A252" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B252" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C252" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="C252" s="9" t="s">
-        <v>566</v>
-      </c>
       <c r="F252" s="13">
         <v>1</v>
       </c>
@@ -14812,7 +14808,7 @@
         <v>1</v>
       </c>
       <c r="I252" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J252" s="4">
         <v>8</v>
@@ -14835,13 +14831,13 @@
     </row>
     <row r="253" spans="1:15">
       <c r="A253" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F253" s="13">
         <v>1</v>
@@ -14850,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="I253" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J253" s="4">
         <v>8</v>
@@ -14873,13 +14869,13 @@
     </row>
     <row r="254" spans="1:15">
       <c r="A254" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F254" s="13">
         <v>1</v>
@@ -14888,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="I254" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J254" s="4">
         <v>8</v>
@@ -14911,22 +14907,22 @@
     </row>
     <row r="255" spans="1:15">
       <c r="A255" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C255" s="9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F255" s="13">
         <v>1</v>
       </c>
       <c r="G255" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J255" s="4">
         <v>8</v>
@@ -14949,28 +14945,28 @@
     </row>
     <row r="256" spans="1:15">
       <c r="A256" s="4" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="C256" s="9" t="s">
-        <v>570</v>
+      <c r="C256" s="10" t="s">
+        <v>575</v>
       </c>
       <c r="F256" s="13">
         <v>1</v>
       </c>
       <c r="G256" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I256" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J256" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K256" s="4" t="s">
-        <v>538</v>
+        <v>582</v>
       </c>
       <c r="L256" s="4" t="s">
         <v>13</v>
@@ -14987,28 +14983,28 @@
     </row>
     <row r="257" spans="1:15">
       <c r="A257" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C257" s="10" t="s">
+      <c r="C257" s="9" t="s">
         <v>577</v>
       </c>
       <c r="F257" s="13">
         <v>1</v>
       </c>
       <c r="G257" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I257" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J257" s="4">
         <v>10</v>
       </c>
       <c r="K257" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L257" s="4" t="s">
         <v>13</v>
@@ -15025,7 +15021,7 @@
     </row>
     <row r="258" spans="1:15">
       <c r="A258" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B258" s="4" t="s">
         <v>578</v>
@@ -15037,16 +15033,16 @@
         <v>1</v>
       </c>
       <c r="G258" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I258" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J258" s="4">
         <v>10</v>
       </c>
       <c r="K258" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L258" s="4" t="s">
         <v>13</v>
@@ -15063,7 +15059,7 @@
     </row>
     <row r="259" spans="1:15">
       <c r="A259" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>580</v>
@@ -15078,13 +15074,13 @@
         <v>1</v>
       </c>
       <c r="I259" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J259" s="4">
         <v>10</v>
       </c>
       <c r="K259" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L259" s="4" t="s">
         <v>13</v>
@@ -15101,34 +15097,34 @@
     </row>
     <row r="260" spans="1:15">
       <c r="A260" s="4" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="B260" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="F260" s="13">
+        <v>1</v>
+      </c>
+      <c r="G260" s="23">
+        <v>1</v>
+      </c>
+      <c r="I260" s="4">
+        <v>1</v>
+      </c>
+      <c r="J260" s="4">
+        <v>11</v>
+      </c>
+      <c r="K260" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="C260" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="F260" s="13">
-        <v>1</v>
-      </c>
-      <c r="G260" s="23">
-        <v>1</v>
-      </c>
-      <c r="I260" s="4">
-        <v>5</v>
-      </c>
-      <c r="J260" s="4">
-        <v>10</v>
-      </c>
-      <c r="K260" s="4" t="s">
-        <v>584</v>
-      </c>
       <c r="L260" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M260" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="N260" s="4">
         <v>1</v>
@@ -15139,28 +15135,28 @@
     </row>
     <row r="261" spans="1:15">
       <c r="A261" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="F261" s="13">
         <v>1</v>
       </c>
       <c r="G261" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J261" s="4">
         <v>11</v>
       </c>
       <c r="K261" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L261" s="4" t="s">
         <v>13</v>
@@ -15175,30 +15171,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15">
+    <row r="262" spans="1:15" ht="18">
       <c r="A262" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="C262" s="27" t="s">
         <v>586</v>
       </c>
-      <c r="B262" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="C262" s="9" t="s">
-        <v>579</v>
-      </c>
       <c r="F262" s="13">
         <v>1</v>
       </c>
       <c r="G262" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I262" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J262" s="4">
         <v>11</v>
       </c>
       <c r="K262" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L262" s="4" t="s">
         <v>13</v>
@@ -15213,15 +15209,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="18">
+    <row r="263" spans="1:15">
       <c r="A263" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C263" s="27" t="s">
-        <v>588</v>
+        <v>592</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>587</v>
       </c>
       <c r="F263" s="13">
         <v>1</v>
@@ -15230,13 +15226,13 @@
         <v>1</v>
       </c>
       <c r="I263" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J263" s="4">
         <v>11</v>
       </c>
       <c r="K263" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L263" s="4" t="s">
         <v>13</v>
@@ -15253,28 +15249,28 @@
     </row>
     <row r="264" spans="1:15">
       <c r="A264" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F264" s="13">
         <v>1</v>
       </c>
       <c r="G264" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J264" s="4">
         <v>11</v>
       </c>
       <c r="K264" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L264" s="4" t="s">
         <v>13</v>
@@ -15291,28 +15287,28 @@
     </row>
     <row r="265" spans="1:15">
       <c r="A265" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F265" s="13">
         <v>1</v>
       </c>
       <c r="G265" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I265" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J265" s="4">
         <v>11</v>
       </c>
       <c r="K265" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L265" s="4" t="s">
         <v>13</v>
@@ -15329,34 +15325,34 @@
     </row>
     <row r="266" spans="1:15">
       <c r="A266" s="4" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="F266" s="13">
         <v>1</v>
       </c>
       <c r="G266" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I266" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J266" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K266" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L266" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M266" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="N266" s="4">
         <v>1</v>
@@ -15367,14 +15363,14 @@
     </row>
     <row r="267" spans="1:15">
       <c r="A267" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C267" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="B267" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="C267" s="9" t="s">
-        <v>599</v>
-      </c>
       <c r="F267" s="13">
         <v>1</v>
       </c>
@@ -15382,13 +15378,13 @@
         <v>0</v>
       </c>
       <c r="I267" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J267" s="4">
         <v>13</v>
       </c>
       <c r="K267" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L267" s="4" t="s">
         <v>13</v>
@@ -15405,10 +15401,10 @@
     </row>
     <row r="268" spans="1:15">
       <c r="A268" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C268" s="9" t="s">
         <v>600</v>
@@ -15420,13 +15416,13 @@
         <v>0</v>
       </c>
       <c r="I268" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J268" s="4">
         <v>13</v>
       </c>
       <c r="K268" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L268" s="4" t="s">
         <v>13</v>
@@ -15443,28 +15439,28 @@
     </row>
     <row r="269" spans="1:15">
       <c r="A269" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C269" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F269" s="13">
         <v>1</v>
       </c>
       <c r="G269" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J269" s="4">
         <v>13</v>
       </c>
       <c r="K269" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L269" s="4" t="s">
         <v>13</v>
@@ -15481,28 +15477,28 @@
     </row>
     <row r="270" spans="1:15">
       <c r="A270" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F270" s="13">
         <v>1</v>
       </c>
       <c r="G270" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J270" s="4">
         <v>13</v>
       </c>
       <c r="K270" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L270" s="4" t="s">
         <v>13</v>
@@ -15519,13 +15515,13 @@
     </row>
     <row r="271" spans="1:15">
       <c r="A271" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F271" s="13">
         <v>1</v>
@@ -15534,13 +15530,13 @@
         <v>0</v>
       </c>
       <c r="I271" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J271" s="4">
         <v>13</v>
       </c>
       <c r="K271" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L271" s="4" t="s">
         <v>13</v>
@@ -15557,14 +15553,14 @@
     </row>
     <row r="272" spans="1:15">
       <c r="A272" s="4" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="B272" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C272" s="9" t="s">
         <v>609</v>
       </c>
-      <c r="C272" s="9" t="s">
-        <v>605</v>
-      </c>
       <c r="F272" s="13">
         <v>1</v>
       </c>
@@ -15572,19 +15568,19 @@
         <v>0</v>
       </c>
       <c r="I272" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J272" s="4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K272" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L272" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M272" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="N272" s="4">
         <v>1</v>
@@ -15593,68 +15589,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" ht="18">
       <c r="A273" s="4" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B273" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C273" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="F273" s="13">
+        <v>1</v>
+      </c>
+      <c r="G273" s="23">
+        <v>1</v>
+      </c>
+      <c r="I273" s="4">
+        <v>4</v>
+      </c>
+      <c r="J273" s="4">
+        <v>10</v>
+      </c>
+      <c r="K273" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="L273" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M273" s="4">
+        <v>2021</v>
+      </c>
+      <c r="N273" s="4">
+        <v>1</v>
+      </c>
+      <c r="O273" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15">
+      <c r="A274" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C274" s="25" t="s">
         <v>612</v>
       </c>
-      <c r="C273" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="F273" s="13">
-        <v>1</v>
-      </c>
-      <c r="G273" s="23">
-        <v>0</v>
-      </c>
-      <c r="I273" s="4">
-        <v>2</v>
-      </c>
-      <c r="J273" s="4">
-        <v>7</v>
-      </c>
-      <c r="K273" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="L273" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M273" s="4">
-        <v>2022</v>
-      </c>
-      <c r="N273" s="4">
-        <v>1</v>
-      </c>
-      <c r="O273" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15" ht="18">
-      <c r="A274" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="B274" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="C274" s="26" t="s">
-        <v>613</v>
-      </c>
       <c r="F274" s="13">
         <v>1</v>
       </c>
       <c r="G274" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I274" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J274" s="4">
         <v>10</v>
       </c>
       <c r="K274" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L274" s="4" t="s">
         <v>13</v>
@@ -15669,16 +15665,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" ht="18">
       <c r="A275" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C275" s="26" t="s">
         <v>617</v>
       </c>
-      <c r="B275" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="C275" s="25" t="s">
-        <v>614</v>
-      </c>
       <c r="F275" s="13">
         <v>1</v>
       </c>
@@ -15686,19 +15682,19 @@
         <v>0</v>
       </c>
       <c r="I275" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J275" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K275" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L275" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M275" s="4">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="N275" s="4">
         <v>1</v>
@@ -15709,14 +15705,14 @@
     </row>
     <row r="276" spans="1:15" ht="18">
       <c r="A276" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C276" s="26" t="s">
         <v>618</v>
       </c>
-      <c r="B276" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C276" s="26" t="s">
-        <v>619</v>
-      </c>
       <c r="F276" s="13">
         <v>1</v>
       </c>
@@ -15724,13 +15720,13 @@
         <v>0</v>
       </c>
       <c r="I276" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J276" s="4">
         <v>17</v>
       </c>
       <c r="K276" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L276" s="4" t="s">
         <v>13</v>
@@ -15747,13 +15743,13 @@
     </row>
     <row r="277" spans="1:15" ht="18">
       <c r="A277" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C277" s="26" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F277" s="13">
         <v>1</v>
@@ -15762,13 +15758,13 @@
         <v>0</v>
       </c>
       <c r="I277" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J277" s="4">
         <v>17</v>
       </c>
       <c r="K277" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L277" s="4" t="s">
         <v>13</v>
@@ -15780,44 +15776,6 @@
         <v>1</v>
       </c>
       <c r="O277" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15" ht="18">
-      <c r="A278" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="C278" s="26" t="s">
-        <v>621</v>
-      </c>
-      <c r="F278" s="13">
-        <v>1</v>
-      </c>
-      <c r="G278" s="23">
-        <v>0</v>
-      </c>
-      <c r="I278" s="4">
-        <v>15</v>
-      </c>
-      <c r="J278" s="4">
-        <v>17</v>
-      </c>
-      <c r="K278" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="L278" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M278" s="4">
-        <v>2019</v>
-      </c>
-      <c r="N278" s="4">
-        <v>1</v>
-      </c>
-      <c r="O278" s="4">
         <v>1</v>
       </c>
     </row>
